--- a/docs/downloads/13/tbl_repondant_alaotra_ambatoharanana.xlsx
+++ b/docs/downloads/13/tbl_repondant_alaotra_ambatoharanana.xlsx
@@ -382,9 +382,6 @@
           <t>Autre</t>
         </is>
       </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -456,9 +453,6 @@
         <is>
           <t>Code NA</t>
         </is>
-      </c>
-      <c r="C7">
-        <v>2</v>
       </c>
     </row>
     <row r="8">
